--- a/forms/trg/Formulir_TRG_corn-rg.xlsx
+++ b/forms/trg/Formulir_TRG_corn-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof (R). Dr. Muhammad Azrai, S.P., M.P.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
@@ -947,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -980,7 +984,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1079,7 +1083,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1112,7 +1116,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1145,7 +1149,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1211,7 +1215,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1302,7 +1306,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1679,7 +1683,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="12" t="n"/>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="12" t="n"/>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="12" t="n"/>
